--- a/per-stock/MKSI/financials.xlsx
+++ b/per-stock/MKSI/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20477353984</v>
+        <v>27447906304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24200353792</v>
+        <v>31170908160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63.29228</v>
+        <v>84.660416</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.62861</v>
+        <v>27.189814</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.027585</v>
+        <v>6.7389903</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>488624992</v>
+        <v>402000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>303.17</v>
+        <v>406.37</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D51</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C51</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B51</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B51:E51)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D49</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C49</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B49</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B49:E49)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1854,13 +2334,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1870,6 +2350,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1880,30 +2361,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1916,21 +2402,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-1941176.470588</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-2730000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-714285.714286</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-972222.222222</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-2583000</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>-630000</v>
+        <v>-2254237.288136</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1939,21 +2426,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.176471</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.119048</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.138889</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.123</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.118644</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1962,21 +2450,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>242000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>232000000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>224000000</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>224000000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>238000000</v>
+        <v>224000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1985,21 +2474,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-13000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-3000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2008,21 +2498,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-13000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-3000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2031,21 +2522,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2054,21 +2546,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>86000000</v>
+        <v>85000000</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>86000000</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>85000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>86000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2077,21 +2570,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>549000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>531000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>504000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>495000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>467000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>468000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2100,21 +2594,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>232000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>229000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>226000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>217000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>203000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>235000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2123,21 +2618,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>147000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>143000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>140000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>130000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>118000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>149000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2146,21 +2642,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-43000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-49000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-51000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-55000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2169,21 +2666,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>58000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>59000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>69000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2192,21 +2690,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>19000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2215,21 +2714,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>93058823.529412</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>117270000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>79285714.285714</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>68027777.777778</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>70417000</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>93370000</v>
+        <v>68745762.71186399</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2238,21 +2738,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2261,21 +2762,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>923000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>877000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>846000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>833000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>807000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>795000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2284,21 +2786,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>143000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>138000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>135000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>111000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>136000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2307,21 +2810,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>71100000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>68000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>67600000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>67400000</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>67700000</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>67700000</v>
       </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2330,21 +2834,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>67300000</v>
+        <v>67400000</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>67300000</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>67300000</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>67200000</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>67400000</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>67400000</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2353,21 +2858,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2376,21 +2882,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2399,21 +2906,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2422,21 +2930,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2445,21 +2954,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2468,21 +2978,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2491,21 +3002,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2514,21 +3026,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-18000000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>10000000</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>10000000</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-11000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2537,21 +3050,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>89000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>84000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>59000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>80000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2560,21 +3074,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-8000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-17000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-4000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2583,21 +3098,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-1000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2606,21 +3122,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-13000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-3000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2632,10 +3149,11 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2646,7 +3164,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2000000</v>
+        <v>8000000</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>2000000</v>
@@ -2655,12 +3173,13 @@
         <v>2000000</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2672,10 +3191,11 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2686,21 +3206,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>11000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>16000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>3000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2709,21 +3230,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-43000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-49000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-51000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-55000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2732,21 +3254,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>58000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>59000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>69000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2755,21 +3278,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>19000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2778,21 +3302,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>155000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>156000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>142000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>140000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>129000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>139000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2801,49 +3326,43 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>352000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>323000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>319000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>313000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>315000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>302000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion Income Statement</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>61000000</v>
-      </c>
+        <v>18000000</v>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization In Income Statement</t>
+          <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -2853,20 +3372,21 @@
         <v>63000000</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>61000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -2876,20 +3396,21 @@
         <v>63000000</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>61000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles Income Statement</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
@@ -2899,160 +3420,191 @@
         <v>63000000</v>
       </c>
       <c r="D45" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>61000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Research And Development</t>
+          <t>Amortization Of Intangibles Income Statement</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>77000000</v>
+        <v>63000000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>76000000</v>
+        <v>63000000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>76000000</v>
+        <v>63000000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>70000000</v>
+        <v>62000000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>65000000</v>
+        <v>60000000</v>
       </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Research And Development</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>185000000</v>
+        <v>81000000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>180000000</v>
+        <v>77000000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>175000000</v>
+        <v>76000000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>185000000</v>
+        <v>76000000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>176000000</v>
+        <v>70000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>479000000</v>
+        <v>190000000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>461000000</v>
+        <v>185000000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>453000000</v>
+        <v>180000000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>444000000</v>
+        <v>175000000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>441000000</v>
+        <v>185000000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>554000000</v>
+        <v>507000000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>527000000</v>
+        <v>479000000</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>520000000</v>
+        <v>461000000</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>492000000</v>
+        <v>453000000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>493000000</v>
+        <v>444000000</v>
       </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Cost Of Revenue</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>1033000000</v>
+        <v>571000000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>988000000</v>
+        <v>554000000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>973000000</v>
+        <v>527000000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>936000000</v>
+        <v>520000000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>934000000</v>
+        <v>492000000</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1078000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1033000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>988000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>973000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>936000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B52" s="3" t="n">
+        <v>1078000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>1033000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>988000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>973000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>936000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>934000000</v>
-      </c>
-      <c r="G51" s="3" t="n"/>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4602,7 +5154,1755 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>67321698</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>67169474</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>67159003</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>67200000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>66900000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>67321698</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>67169474</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>67159003</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>67200000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>66900000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3479000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3526000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3607000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3734000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>3804000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4292000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4447000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4585000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4697000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4701000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-1819000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-1995000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-2159000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-2284000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-2380000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6859000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6920000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>6904000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6961000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6813000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>254000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1583000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1652000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1645000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-1819000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-1995000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-2159000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-2284000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-2380000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>246000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>281000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>289000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>242000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2811000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2719000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2553000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2354000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5461000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6869000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>6853000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>6910000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>6763000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2811000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2719000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2553000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2354000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2811000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2719000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2553000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2354000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-93000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-108000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-84000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-225000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-93000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-108000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-84000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-225000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>778000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>711000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>618000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>559000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>512000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2104000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2101000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2090000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2078000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2067000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>5917000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6077000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6177000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>6273000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>6202000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>3626000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>5150000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>5291000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5441000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5421000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>131000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>151000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>146000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>139000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>474000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>483000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>504000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>502000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>474000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>483000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>504000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>502000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2894000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4396000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>4503000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>4615000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>4620000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>246000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>258000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>2650000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4150000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4253000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>4357000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>4409000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2291000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>927000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>886000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>832000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>781000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>98000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>101000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>79000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>101000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>79000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1398000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1398000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1398000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>143000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>153000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>143000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>583000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>533000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>443000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>389000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>83000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>455000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>443000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>389000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>61000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>61000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>448000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>407000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>382000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>355000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>8728000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>8796000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>8777000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>8826000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>8556000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>6183000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>6286000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>6241000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>6342000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>6130000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>491000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>492000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>438000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>421000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>4630000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4714000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>4759000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>4837000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>4734000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2065000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2140000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>2196000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2267000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2238000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2565000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2574000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2563000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2570000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2496000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1062000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1080000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1044000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1084000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1013000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n">
+        <v>-859000000</v>
+      </c>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>-736000000</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1062000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1939000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1044000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1084000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1013000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>183000000</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>147000000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>1062000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>270000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1044000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1084000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1013000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>867000000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>840000000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>379000000</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>322000000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2545000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>2510000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2536000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>2484000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2426000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>252000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>263000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>238000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>949000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>921000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>934000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>918000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>894000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>196000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>188000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>188000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>171000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>153000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>131000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>114000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>622000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>617000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>632000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>642000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>634000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>775000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>651000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>611000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>649000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>639000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>775000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>651000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>611000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>649000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>639000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>780000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>616000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>655000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>645000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>569000000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>675000000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>697000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>674000000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>655000000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>569000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>675000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>697000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>674000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>655000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5954,13 +8254,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5970,6 +8270,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5980,30 +8281,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6016,21 +8322,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>92000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>146000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>136000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>123000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>125000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6048,10 +8355,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6060,21 +8370,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-113000000</v>
+        <v>-1274000000</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-113000000</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>-113000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-113000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-229000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6083,7 +8394,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1192000000</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -6098,6 +8409,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6106,21 +8418,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-51000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-29000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6129,21 +8442,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>569000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>675000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>697000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>674000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>655000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>714000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6152,21 +8466,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>675000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>697000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>674000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>655000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>714000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>861000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6175,21 +8490,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-26000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6198,21 +8514,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-109000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-32000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-57000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-121000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6221,21 +8538,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-137000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-125000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-128000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-129000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-180000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-246000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6244,21 +8562,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-137000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-125000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-128000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-129000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-180000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-246000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6267,21 +8586,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-22000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="3" t="n">
-        <v>-2000000</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>-2000000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-5000000</v>
+        <v>-2000000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6290,21 +8610,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>3000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6313,13 +8634,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-17000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-14000000</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>-15000000</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>-15000000</v>
@@ -6328,6 +8649,7 @@
         <v>-15000000</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6336,13 +8658,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-17000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-14000000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>-15000000</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-15000000</v>
@@ -6351,6 +8673,7 @@
         <v>-15000000</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6368,10 +8691,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6389,10 +8715,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6401,21 +8730,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-113000000</v>
+        <v>-82000000</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>-113000000</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v>-113000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-113000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-229000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6424,21 +8754,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-113000000</v>
+        <v>-82000000</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-113000000</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>-113000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-113000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-229000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6447,21 +8778,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-113000000</v>
+        <v>-1274000000</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>-113000000</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>-113000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-113000000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-229000000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6470,7 +8802,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0</v>
+        <v>1192000000</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -6485,6 +8817,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6493,21 +8826,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-49000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-51000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6516,21 +8850,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-49000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-51000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6539,21 +8874,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-50000000</v>
+        <v>-25000000</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-50000000</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v>-50000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6561,18 +8897,19 @@
           <t>Sale Of PPE</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6583,21 +8920,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-51000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-29000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6606,21 +8944,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>142000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>197000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>141000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>176000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6629,21 +8968,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>142000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>197000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>141000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>176000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6652,21 +8992,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0</v>
+        <v>-134000000</v>
       </c>
       <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>58000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>27000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>5000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6675,21 +9016,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>-9000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-15000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6698,21 +9040,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>8000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6721,21 +9064,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>53000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>64000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6744,21 +9088,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-68000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>28000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n">
-        <v>22000000</v>
-      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6767,21 +9112,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>29000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-8000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>38000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6790,21 +9136,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>27000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>42000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6813,21 +9160,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>12000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-4000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6836,21 +9184,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>12000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-4000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6859,21 +9208,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-49000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-30000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>-12000000</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>-12000000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>9000000</v>
+        <v>-12000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6882,21 +9232,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-129000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-40000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-19000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-29000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6905,21 +9256,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-129000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-40000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-19000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-29000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6928,21 +9280,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>10000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6951,21 +9304,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>9000000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>12000000</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>12000000</v>
       </c>
       <c r="E43" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>11000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6974,21 +9328,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>8000000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>10000000</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>10000000</v>
       </c>
       <c r="E44" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>15000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7000,10 +9355,11 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7014,21 +9370,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>-24000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-71000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-43000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-58000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7037,21 +9394,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-24000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-71000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-43000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-58000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7060,21 +9418,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>86000000</v>
+        <v>85000000</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>86000000</v>
       </c>
       <c r="D48" s="3" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>85000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>86000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7083,21 +9442,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>86000000</v>
+        <v>85000000</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>86000000</v>
       </c>
       <c r="D49" s="3" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>85000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>86000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7106,21 +9466,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>16000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7128,22 +9489,23 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>-8000000</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>2000000</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>2000000</v>
       </c>
       <c r="F51" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G51" s="3" t="n">
         <v>11000000</v>
       </c>
-      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7155,10 +9517,11 @@
       <c r="C52" s="3" t="n"/>
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7167,28 +9530,29 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>107000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
